--- a/2026/DRAGO/Junio/EXPENSAS-Junio.xlsx
+++ b/2026/DRAGO/Junio/EXPENSAS-Junio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\DRAGO\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\DRAGO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE91015C-F87E-47E2-BE65-D528E6FA227D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EB28E7-DD53-4BDD-9A23-D8AB4A6643B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -225,9 +225,6 @@
     <t xml:space="preserve">TOTAL GASTOS ORDINARIOS (A) </t>
   </si>
   <si>
-    <t>Prevision ord</t>
-  </si>
-  <si>
     <t>Expensas ordinarias</t>
   </si>
   <si>
@@ -282,15 +279,6 @@
     <t>Deuda o saldo a favor</t>
   </si>
   <si>
-    <t>Vto. 18/06</t>
-  </si>
-  <si>
-    <t>LIQUIDACIÓN EXPENSAS MAYO 2025</t>
-  </si>
-  <si>
-    <t>Cittadino Jazmin - Cerrajeria Citta - Destrabe llave cilindro 19/05</t>
-  </si>
-  <si>
     <t>Alterini Guido - Mantenimiento</t>
   </si>
   <si>
@@ -301,6 +289,18 @@
   </si>
   <si>
     <t xml:space="preserve">Sueldo Sra. Karina </t>
+  </si>
+  <si>
+    <t>Citta Jazmin - Cierre por puerta defectuoso</t>
+  </si>
+  <si>
+    <t>Vto. 17/07</t>
+  </si>
+  <si>
+    <t>Prevision ordinaria - Limpieza tanque de agua</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS JUNIO 2026</t>
   </si>
 </sst>
 </file>
@@ -840,7 +840,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1007,6 +1007,12 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1063,9 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1506,10 +1509,10 @@
         <v>35</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1560,7 +1563,7 @@
         <v>49</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" s="106">
         <v>48091.199999999997</v>
@@ -1570,10 +1573,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B18" s="55"/>
-      <c r="C18" s="106">
+      <c r="C18" s="109">
         <v>5837.2</v>
       </c>
       <c r="D18" s="38"/>
@@ -1587,7 +1590,7 @@
         <v>61</v>
       </c>
       <c r="C19" s="106">
-        <v>22832.87</v>
+        <v>26065.15</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="12"/>
@@ -1599,9 +1602,8 @@
         <v>31</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="127">
-        <f>17457+197644.67</f>
-        <v>215101.67</v>
+      <c r="C20" s="108">
+        <v>200224.34</v>
       </c>
       <c r="D20" s="38"/>
       <c r="F20" s="12"/>
@@ -1620,7 +1622,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="12"/>
       <c r="H21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1628,7 +1630,7 @@
       <c r="B22" s="58"/>
       <c r="C22" s="42">
         <f>SUM(C17:C21)</f>
-        <v>352362.94</v>
+        <v>340717.89</v>
       </c>
       <c r="E22" s="86"/>
     </row>
@@ -1641,17 +1643,17 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="46" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B24" s="59"/>
       <c r="C24" s="106">
-        <v>89000</v>
+        <v>110000</v>
       </c>
       <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="106">
@@ -1661,7 +1663,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="106">
@@ -1671,30 +1673,32 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="59"/>
       <c r="C27" s="106">
-        <v>55000</v>
+        <v>120000</v>
       </c>
       <c r="F27" s="18"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="59"/>
       <c r="C28" s="106">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B29" s="56"/>
-      <c r="C29" s="52"/>
+      <c r="C29" s="52">
+        <v>250000</v>
+      </c>
       <c r="D29" s="5"/>
       <c r="E29" s="12"/>
       <c r="F29" s="18"/>
@@ -1704,7 +1708,7 @@
       <c r="B30" s="58"/>
       <c r="C30" s="42">
         <f>SUM(C23:C29)</f>
-        <v>281000</v>
+        <v>641200</v>
       </c>
       <c r="F30" s="18"/>
     </row>
@@ -1715,7 +1719,7 @@
       <c r="B31" s="49"/>
       <c r="C31" s="60">
         <f>+C30+C22</f>
-        <v>633362.93999999994</v>
+        <v>981917.89</v>
       </c>
       <c r="F31" s="18"/>
     </row>
@@ -1731,8 +1735,8 @@
       <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="108"/>
-      <c r="B34" s="109"/>
+      <c r="A34" s="110"/>
+      <c r="B34" s="111"/>
       <c r="C34" s="100"/>
       <c r="F34" s="18"/>
     </row>
@@ -1770,7 +1774,7 @@
       <c r="B40" s="29"/>
       <c r="C40" s="30">
         <f>+C38+C31</f>
-        <v>633362.93999999994</v>
+        <v>981917.89</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="33">
-        <v>-199790.02378991072</v>
+        <v>-371918.23442988831</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -1795,14 +1799,14 @@
       </c>
       <c r="C44" s="27">
         <f>'prorrateo '!F13</f>
-        <v>461234.72936002235</v>
+        <v>849511.80101037957</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C45" s="105">
         <f>extraordinarias!E13</f>
@@ -1813,7 +1817,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" s="105">
         <f>-C38</f>
@@ -1828,7 +1832,7 @@
       </c>
       <c r="C47" s="61">
         <f>-(C31-C29)</f>
-        <v>-633362.93999999994</v>
+        <v>-731917.89</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1838,7 +1842,7 @@
       <c r="B48" s="28"/>
       <c r="C48" s="33">
         <f>SUM(C43:C47)</f>
-        <v>-371918.23442988831</v>
+        <v>-254324.32341950876</v>
       </c>
       <c r="D48" s="6"/>
     </row>
@@ -1945,17 +1949,17 @@
         <v>47</v>
       </c>
       <c r="E1" s="102">
-        <v>633362.93999999994</v>
+        <v>981917.89</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 18/06</v>
+        <v>Vto. 17/07</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
-        <v>LIQUIDACIÓN EXPENSAS MAYO 2025</v>
+        <v>LIQUIDACIÓN EXPENSAS JUNIO 2026</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="72"/>
@@ -1973,58 +1977,58 @@
       <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="113"/>
-      <c r="B3" s="111" t="s">
+      <c r="A3" s="115"/>
+      <c r="B3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="111" t="s">
+      <c r="E3" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="119" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="117" t="s">
+      <c r="G3" s="121" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="120" t="s">
+      <c r="I3" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="K3" s="115" t="s">
+      <c r="J3" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="117" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="115" t="s">
+      <c r="M3" s="117" t="s">
         <v>66</v>
       </c>
-      <c r="M3" s="115" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="114"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
@@ -2040,14 +2044,15 @@
         <v>56</v>
       </c>
       <c r="E5" s="37">
-        <v>64621.710639999968</v>
+        <v>76428.626379999972</v>
       </c>
       <c r="F5" s="85">
-        <v>64830</v>
+        <f t="shared" ref="F5:F12" si="0">E5</f>
+        <v>76428.626379999972</v>
       </c>
       <c r="G5" s="37">
         <f>E5-F5</f>
-        <v>-208.28936000003159</v>
+        <v>0</v>
       </c>
       <c r="H5" s="37">
         <f>IF(G5&gt;0,G5*3%,0)</f>
@@ -2059,15 +2064,15 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>76636.915739999997</v>
+        <v>118812.06469</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>76428.626379999972</v>
+        <v>118812.06469</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>79485.771435199975</v>
+        <v>123564.5472776</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2084,18 +2089,18 @@
         <v>57</v>
       </c>
       <c r="E6" s="37">
-        <v>65365.616279999995</v>
+        <v>77270.278679999989</v>
       </c>
       <c r="F6" s="85">
-        <f>E6</f>
-        <v>65365.616279999995</v>
+        <f t="shared" si="0"/>
+        <v>77270.278679999989</v>
       </c>
       <c r="G6" s="37">
-        <f t="shared" ref="G6:G12" si="0">E6-F6</f>
+        <f t="shared" ref="G6:G12" si="1">E6-F6</f>
         <v>0</v>
       </c>
       <c r="H6" s="37">
-        <f t="shared" ref="H6:H12" si="1">IF(G6&gt;0,G6*3%,0)</f>
+        <f t="shared" ref="H6:H12" si="2">IF(G6&gt;0,G6*3%,0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="74">
@@ -2104,15 +2109,15 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>77270.278679999989</v>
+        <v>119793.98258</v>
       </c>
       <c r="L6" s="75">
-        <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
-        <v>77270.278679999989</v>
+        <f t="shared" ref="L6:L12" si="3">E6-F6+H6+K6+J6</f>
+        <v>119793.98258</v>
       </c>
       <c r="M6" s="76">
-        <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
-        <v>80361.08982719999</v>
+        <f t="shared" ref="M6:M12" si="4">L6+L6*4%</f>
+        <v>124585.7418832</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
@@ -2128,22 +2133,21 @@
         <v>28</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="85">
-        <f>65194.64</f>
-        <v>65194.64</v>
+        <v>77067.600000000006</v>
       </c>
       <c r="F7" s="85">
-        <f>65194.64</f>
-        <v>65194.64</v>
+        <f t="shared" si="0"/>
+        <v>77067.600000000006</v>
       </c>
       <c r="G7" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H7" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="74">
@@ -2152,15 +2156,15 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>74103.46398</v>
+        <v>114884.39313000001</v>
       </c>
       <c r="L7" s="75">
-        <f t="shared" si="2"/>
-        <v>74103.46398</v>
+        <f t="shared" si="3"/>
+        <v>114884.39313000001</v>
       </c>
       <c r="M7" s="76">
-        <f t="shared" si="3"/>
-        <v>77067.602539200001</v>
+        <f t="shared" si="4"/>
+        <v>119479.76885520002</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2174,21 +2178,21 @@
         <v>29</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" s="85">
-        <v>62686.69758</v>
+        <v>74103.46398</v>
       </c>
       <c r="F8" s="85">
-        <f>E8</f>
-        <v>62686.69758</v>
+        <f t="shared" si="0"/>
+        <v>74103.46398</v>
       </c>
       <c r="G8" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="74">
@@ -2197,18 +2201,18 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>74103.46398</v>
+        <v>114884.39313000001</v>
       </c>
       <c r="L8" s="75">
-        <f t="shared" si="2"/>
-        <v>74103.46398</v>
+        <f t="shared" si="3"/>
+        <v>114884.39313000001</v>
       </c>
       <c r="M8" s="76">
-        <f t="shared" si="3"/>
-        <v>77067.602539200001</v>
+        <f t="shared" si="4"/>
+        <v>119479.76885520002</v>
       </c>
       <c r="N8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2225,18 +2229,18 @@
         <v>55</v>
       </c>
       <c r="E9" s="37">
-        <v>73402.372380000001</v>
+        <v>86770.722779999996</v>
       </c>
       <c r="F9" s="85">
-        <f>E9</f>
-        <v>73402.372380000001</v>
+        <f t="shared" si="0"/>
+        <v>86770.722779999996</v>
       </c>
       <c r="G9" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="74">
@@ -2245,15 +2249,15 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>86770.722779999996</v>
+        <v>134522.75093000001</v>
       </c>
       <c r="L9" s="75">
-        <f t="shared" si="2"/>
-        <v>86770.722779999996</v>
+        <f t="shared" si="3"/>
+        <v>134522.75093000001</v>
       </c>
       <c r="M9" s="76">
-        <f t="shared" si="3"/>
-        <v>90241.551691200002</v>
+        <f t="shared" si="4"/>
+        <v>139903.6609672</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2267,21 +2271,21 @@
         <v>26</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" s="37">
-        <v>61710.868140022387</v>
+        <v>83603.908079999994</v>
       </c>
       <c r="F10" s="85">
-        <f>E10</f>
-        <v>61710.868140022387</v>
+        <f t="shared" si="0"/>
+        <v>83603.908079999994</v>
       </c>
       <c r="G10" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H10" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I10" s="74">
@@ -2290,15 +2294,15 @@
       <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>83603.908079999994</v>
+        <v>129613.16148000001</v>
       </c>
       <c r="L10" s="75">
-        <f t="shared" si="2"/>
-        <v>83603.908079999994</v>
+        <f t="shared" si="3"/>
+        <v>129613.16148000001</v>
       </c>
       <c r="M10" s="76">
-        <f t="shared" si="3"/>
-        <v>86948.064403199998</v>
+        <f t="shared" si="4"/>
+        <v>134797.6879392</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2313,16 +2317,19 @@
       </c>
       <c r="D11" s="41"/>
       <c r="E11" s="37">
-        <v>207177.68383532</v>
-      </c>
-      <c r="F11" s="85"/>
+        <v>293830.10773037962</v>
+      </c>
+      <c r="F11" s="85">
+        <f t="shared" si="0"/>
+        <v>293830.10773037962</v>
+      </c>
       <c r="G11" s="37">
-        <f t="shared" si="0"/>
-        <v>207177.68383532</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H11" s="37">
-        <f t="shared" si="1"/>
-        <v>6215.3305150595997</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I11" s="74">
         <v>0.127</v>
@@ -2330,15 +2337,15 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>80437.093379999991</v>
+        <v>124703.57203000001</v>
       </c>
       <c r="L11" s="75">
-        <f t="shared" si="2"/>
-        <v>293830.10773037962</v>
+        <f t="shared" si="3"/>
+        <v>124703.57203000001</v>
       </c>
       <c r="M11" s="76">
-        <f t="shared" si="3"/>
-        <v>305583.31203959481</v>
+        <f t="shared" si="4"/>
+        <v>129691.7149112</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2355,18 +2362,18 @@
         <v>54</v>
       </c>
       <c r="E12" s="37">
-        <v>68044.534979999997</v>
+        <v>80437.093379999991</v>
       </c>
       <c r="F12" s="85">
-        <f>E12</f>
-        <v>68044.534979999997</v>
+        <f t="shared" si="0"/>
+        <v>80437.093379999991</v>
       </c>
       <c r="G12" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H12" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="74">
@@ -2375,15 +2382,15 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>80437.093379999991</v>
+        <v>124703.57203000001</v>
       </c>
       <c r="L12" s="75">
-        <f t="shared" si="2"/>
-        <v>80437.093379999991</v>
+        <f t="shared" si="3"/>
+        <v>124703.57203000001</v>
       </c>
       <c r="M12" s="76">
-        <f t="shared" si="3"/>
-        <v>83654.577115199994</v>
+        <f t="shared" si="4"/>
+        <v>129691.7149112</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2395,19 +2402,19 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>668204.12383534235</v>
+        <v>849511.80101037957</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
-        <v>461234.72936002235</v>
+        <v>849511.80101037957</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>6215.3305150595997</v>
+        <v>0</v>
       </c>
       <c r="I13" s="70">
-        <f t="shared" ref="I13" si="4">SUM(I5:I12)</f>
+        <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
         <v>1</v>
       </c>
       <c r="J13" s="101">
@@ -2416,61 +2423,61 @@
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>633362.93999999994</v>
+        <v>981917.89</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>846547.66499037948</v>
+        <v>981917.89</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>880409.57158999471</v>
+        <v>1021194.6056</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C15" s="110" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
+      <c r="C15" s="112" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
     </row>
     <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
     </row>
     <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
       <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2480,16 +2487,16 @@
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
@@ -2497,16 +2504,16 @@
     <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
@@ -2518,16 +2525,16 @@
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
@@ -2540,16 +2547,16 @@
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
@@ -2562,16 +2569,16 @@
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="110"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="110"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
@@ -2584,16 +2591,16 @@
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
@@ -2606,16 +2613,16 @@
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
@@ -2628,16 +2635,16 @@
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
@@ -2650,16 +2657,16 @@
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
@@ -2672,16 +2679,16 @@
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="110"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
@@ -2692,68 +2699,68 @@
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="112"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="112"/>
+      <c r="K28" s="112"/>
+      <c r="L28" s="112"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="112"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="110"/>
-      <c r="L30" s="110"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="112"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="112"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="112"/>
+      <c r="J30" s="112"/>
+      <c r="K30" s="112"/>
+      <c r="L30" s="112"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="110"/>
-      <c r="L31" s="110"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="110"/>
-      <c r="G32" s="110"/>
-      <c r="H32" s="110"/>
-      <c r="I32" s="110"/>
-      <c r="J32" s="110"/>
-      <c r="K32" s="110"/>
-      <c r="L32" s="110"/>
+      <c r="C32" s="112"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="112"/>
+      <c r="H32" s="112"/>
+      <c r="I32" s="112"/>
+      <c r="J32" s="112"/>
+      <c r="K32" s="112"/>
+      <c r="L32" s="112"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="39"/>
@@ -2803,10 +2810,10 @@
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="122">
-        <v>0</v>
-      </c>
-      <c r="E1" s="122"/>
+      <c r="D1" s="124">
+        <v>0</v>
+      </c>
+      <c r="E1" s="124"/>
       <c r="F1" s="103"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
@@ -2816,7 +2823,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="88"/>
       <c r="C2" s="89"/>
@@ -2832,49 +2839,49 @@
       <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="111" t="s">
+      <c r="A3" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="111" t="s">
+      <c r="C3" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="120" t="s">
+      <c r="E3" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="111" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="119" t="s">
+      <c r="F3" s="113" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="121" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="120" t="s">
+      <c r="H3" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="126" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="125" t="s">
+      <c r="I3" s="128" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="127" t="s">
         <v>52</v>
       </c>
       <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="124"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="125"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="127"/>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
